--- a/tablica.xlsx
+++ b/tablica.xlsx
@@ -18,7 +18,6 @@
   <si>
     <t>введите целое число а</t>
   </si>
-  <si/>
   <si>
     <r>
       <rPr>
@@ -73,19 +72,6 @@
     </r>
   </si>
   <si>
-    <t>показатель</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="XO Thames"/>
-        <b val="true"/>
-        <sz val="12"/>
-      </rPr>
-      <t>степень(1)</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="XO Thames"/>
@@ -130,6 +116,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
+  <numFmts>
+    <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1000"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -177,15 +166,15 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf applyBorder="false" applyFill="false" applyFont="true" borderId="0" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
+    <xf applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="0" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf applyBorder="false" applyFill="false" applyFont="true" borderId="0" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
-    <xf applyBorder="false" applyFill="false" applyFont="true" borderId="0" fillId="0" fontId="2" numFmtId="0" quotePrefix="false"/>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" borderId="0" fillId="0" fontId="1" numFmtId="0" quotePrefix="false">
+    <xf applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="0" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false"/>
+    <xf applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="0" fillId="0" fontId="2" numFmtId="1000" quotePrefix="false"/>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="0" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyBorder="true" applyFill="false" applyFont="true" borderId="1" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
+    <xf applyBorder="true" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="1" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle builtinId="0" name="Normal" xfId="0"/>
@@ -424,22 +413,20 @@
       </c>
     </row>
     <row outlineLevel="0" r="2">
-      <c r="C2" s="0" t="s">
-        <v>1</v>
-      </c>
+      <c r="C2" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="4">
       <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
@@ -1269,7 +1256,7 @@
   <sheetData>
     <row customHeight="true" ht="22.499998092651367" outlineLevel="0" r="1">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="0" t="n">
         <v>9</v>
@@ -1277,7 +1264,7 @@
     </row>
     <row outlineLevel="0" r="2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="0" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">2^(B1+1)-1</f>
@@ -1302,462 +1289,215 @@
   </cols>
   <sheetData>
     <row outlineLevel="0" r="1">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="n">
-        <v>3</v>
-      </c>
+      <c r="A1" s="0" t="n"/>
+      <c r="B1" s="0" t="n"/>
+      <c r="C1" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="2">
       <c r="B2" s="0" t="n"/>
-      <c r="C2" s="0" t="s">
-        <v>1</v>
-      </c>
+      <c r="C2" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="3">
       <c r="B3" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="4">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="n"/>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
-      <c r="A5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A5</f>
-        <v>1</v>
-      </c>
+      <c r="A5" s="0" t="n"/>
+      <c r="B5" s="0" t="n"/>
       <c r="D5" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MAX(B:B)</f>
+        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">MAX('Лист1'!B:B)</f>
         <v>8.8629381196525014E+21</v>
       </c>
     </row>
     <row outlineLevel="0" r="6">
-      <c r="A6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A6</f>
-        <v>3</v>
-      </c>
+      <c r="A6" s="0" t="n"/>
+      <c r="B6" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="7">
-      <c r="A7" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A7</f>
-        <v>9</v>
-      </c>
+      <c r="A7" s="0" t="n"/>
+      <c r="B7" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="8">
-      <c r="A8" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A8</f>
-        <v>27</v>
-      </c>
+      <c r="A8" s="0" t="n"/>
+      <c r="B8" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="9">
-      <c r="A9" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A9</f>
-        <v>81</v>
-      </c>
+      <c r="A9" s="0" t="n"/>
+      <c r="B9" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="10">
-      <c r="A10" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A10</f>
-        <v>243</v>
-      </c>
+      <c r="A10" s="0" t="n"/>
+      <c r="B10" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="11">
-      <c r="A11" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A11</f>
-        <v>729</v>
-      </c>
+      <c r="A11" s="0" t="n"/>
+      <c r="B11" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="12">
-      <c r="A12" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A12</f>
-        <v>2187</v>
-      </c>
+      <c r="A12" s="0" t="n"/>
+      <c r="B12" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="13">
-      <c r="A13" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A13</f>
-        <v>6561</v>
-      </c>
+      <c r="A13" s="0" t="n"/>
+      <c r="B13" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="14">
-      <c r="A14" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A14</f>
-        <v>19683</v>
-      </c>
+      <c r="A14" s="0" t="n"/>
+      <c r="B14" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="15">
-      <c r="A15" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A15</f>
-        <v>59049</v>
-      </c>
+      <c r="A15" s="0" t="n"/>
+      <c r="B15" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="16">
-      <c r="A16" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A16</f>
-        <v>177147</v>
-      </c>
+      <c r="A16" s="0" t="n"/>
+      <c r="B16" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="17">
-      <c r="A17" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A17</f>
-        <v>531441</v>
-      </c>
+      <c r="A17" s="0" t="n"/>
+      <c r="B17" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="18">
-      <c r="A18" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A18</f>
-        <v>1594323</v>
-      </c>
+      <c r="A18" s="0" t="n"/>
+      <c r="B18" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="19">
-      <c r="A19" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A19</f>
-        <v>4782969</v>
-      </c>
+      <c r="A19" s="0" t="n"/>
+      <c r="B19" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="20">
-      <c r="A20" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A20</f>
-        <v>14348907</v>
-      </c>
+      <c r="A20" s="0" t="n"/>
+      <c r="B20" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="21">
-      <c r="A21" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="B21" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A21</f>
-        <v>43046721</v>
-      </c>
+      <c r="A21" s="0" t="n"/>
+      <c r="B21" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="22">
-      <c r="A22" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="B22" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A22</f>
-        <v>129140163</v>
-      </c>
+      <c r="A22" s="0" t="n"/>
+      <c r="B22" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="23">
-      <c r="A23" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="B23" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A23</f>
-        <v>387420489</v>
-      </c>
+      <c r="A23" s="0" t="n"/>
+      <c r="B23" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="24">
-      <c r="A24" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="B24" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A24</f>
-        <v>1162261467</v>
-      </c>
+      <c r="A24" s="0" t="n"/>
+      <c r="B24" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="25">
-      <c r="A25" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="B25" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A25</f>
-        <v>3486784401</v>
-      </c>
+      <c r="A25" s="0" t="n"/>
+      <c r="B25" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="26">
-      <c r="A26" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="B26" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A26</f>
-        <v>10460353203</v>
-      </c>
+      <c r="A26" s="0" t="n"/>
+      <c r="B26" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="27">
-      <c r="A27" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="B27" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A27</f>
-        <v>31381059609</v>
-      </c>
+      <c r="A27" s="0" t="n"/>
+      <c r="B27" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="28">
-      <c r="A28" s="0" t="n">
-        <v>23</v>
-      </c>
-      <c r="B28" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A28</f>
-        <v>94143178827</v>
-      </c>
+      <c r="A28" s="0" t="n"/>
+      <c r="B28" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="29">
-      <c r="A29" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="B29" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A29</f>
-        <v>282429536481</v>
-      </c>
+      <c r="A29" s="0" t="n"/>
+      <c r="B29" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="30">
-      <c r="A30" s="0" t="n">
-        <v>25</v>
-      </c>
-      <c r="B30" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A30</f>
-        <v>847288609443</v>
-      </c>
+      <c r="A30" s="0" t="n"/>
+      <c r="B30" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="31">
-      <c r="A31" s="0" t="n">
-        <v>26</v>
-      </c>
-      <c r="B31" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A31</f>
-        <v>2541865828329</v>
-      </c>
+      <c r="A31" s="0" t="n"/>
+      <c r="B31" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="32">
-      <c r="A32" s="0" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A32</f>
-        <v>7625597484987</v>
-      </c>
+      <c r="A32" s="0" t="n"/>
+      <c r="B32" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="33">
-      <c r="A33" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A33</f>
-        <v>22876792454961</v>
-      </c>
+      <c r="A33" s="0" t="n"/>
+      <c r="B33" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="34">
-      <c r="A34" s="0" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A34</f>
-        <v>68630377364883</v>
-      </c>
+      <c r="A34" s="0" t="n"/>
+      <c r="B34" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="35">
-      <c r="A35" s="0" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A35</f>
-        <v>205891132094649</v>
-      </c>
+      <c r="A35" s="0" t="n"/>
+      <c r="B35" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="36">
-      <c r="A36" s="0" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A36</f>
-        <v>617673396283947</v>
-      </c>
+      <c r="A36" s="0" t="n"/>
+      <c r="B36" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="37">
-      <c r="A37" s="0" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A37</f>
-        <v>1853020188851841</v>
-      </c>
+      <c r="A37" s="0" t="n"/>
+      <c r="B37" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="38">
-      <c r="A38" s="0" t="n">
-        <v>33</v>
-      </c>
-      <c r="B38" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A38</f>
-        <v>5559060566555523</v>
-      </c>
+      <c r="A38" s="0" t="n"/>
+      <c r="B38" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="39">
-      <c r="A39" s="0" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A39</f>
-        <v>16677181699666570</v>
-      </c>
+      <c r="A39" s="0" t="n"/>
+      <c r="B39" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="40">
-      <c r="A40" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="B40" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A40</f>
-        <v>50031545098999704</v>
-      </c>
+      <c r="A40" s="0" t="n"/>
+      <c r="B40" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="41">
-      <c r="A41" s="0" t="n">
-        <v>36</v>
-      </c>
-      <c r="B41" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A41</f>
-        <v>1.5009463529699914E+17</v>
-      </c>
+      <c r="A41" s="0" t="n"/>
+      <c r="B41" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="42">
-      <c r="A42" s="0" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A42</f>
-        <v>4.5028390589099738E+17</v>
-      </c>
+      <c r="A42" s="0" t="n"/>
+      <c r="B42" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="43">
-      <c r="A43" s="0" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A43</f>
-        <v>1.350851717672992E+18</v>
-      </c>
+      <c r="A43" s="0" t="n"/>
+      <c r="B43" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="44">
-      <c r="A44" s="0" t="n">
-        <v>39</v>
-      </c>
-      <c r="B44" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A44</f>
-        <v>4.0525551530189763E+18</v>
-      </c>
+      <c r="A44" s="0" t="n"/>
+      <c r="B44" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="45">
-      <c r="A45" s="0" t="n">
-        <v>40</v>
-      </c>
-      <c r="B45" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A45</f>
-        <v>1.2157665459056929E+19</v>
-      </c>
+      <c r="A45" s="0" t="n"/>
+      <c r="B45" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="46">
-      <c r="A46" s="0" t="n">
-        <v>41</v>
-      </c>
-      <c r="B46" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A46</f>
-        <v>3.6472996377170788E+19</v>
-      </c>
+      <c r="A46" s="0" t="n"/>
+      <c r="B46" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="47">
-      <c r="A47" s="0" t="n">
-        <v>42</v>
-      </c>
-      <c r="B47" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A47</f>
-        <v>1.0941898913151237E+20</v>
-      </c>
+      <c r="A47" s="0" t="n"/>
+      <c r="B47" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="48">
-      <c r="A48" s="0" t="n">
-        <v>43</v>
-      </c>
-      <c r="B48" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A48</f>
-        <v>3.2825696739453705E+20</v>
-      </c>
+      <c r="A48" s="0" t="n"/>
+      <c r="B48" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="49">
-      <c r="A49" s="0" t="n">
-        <v>44</v>
-      </c>
-      <c r="B49" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A49</f>
-        <v>9.847709021836112E+20</v>
-      </c>
+      <c r="A49" s="0" t="n"/>
+      <c r="B49" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="50">
-      <c r="A50" s="0" t="n">
-        <v>45</v>
-      </c>
-      <c r="B50" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A50</f>
-        <v>2.9543127065508336E+21</v>
-      </c>
+      <c r="A50" s="0" t="n"/>
+      <c r="B50" s="0" t="n"/>
     </row>
     <row outlineLevel="0" r="51">
-      <c r="A51" s="0" t="n">
-        <v>46</v>
-      </c>
-      <c r="B51" s="0" t="n">
-        <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">$C$1^A51</f>
-        <v>8.8629381196525014E+21</v>
-      </c>
+      <c r="A51" s="0" t="n"/>
+      <c r="B51" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.59055554866790771" footer="0.5" header="0.5" left="0.59055554866790771" right="0.59055554866790771" top="0.59055554866790771"/>
@@ -1778,7 +1518,7 @@
   <sheetData>
     <row outlineLevel="0" r="1">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="n"/>
     </row>
@@ -1848,12 +1588,12 @@
     </row>
     <row outlineLevel="0" r="4">
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row outlineLevel="0" r="6">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="n">
         <f aca="false" ca="false" dt2D="false" dtr="false" t="normal">A2*512+B2*256+C2*128+D2*64+E2*32+F2*16+G2*8+H2*4+I2*2+J2*1</f>
